--- a/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años)</t>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,49; 72,97</t>
+          <t>50,88; 72,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,35; 77,21</t>
+          <t>58,28; 77,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,75; 72,9</t>
+          <t>57,68; 72,67</t>
         </is>
       </c>
     </row>
@@ -621,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>64,7; 85,3</t>
+          <t>66,8; 85,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>66,85; 87,92</t>
+          <t>67,15; 87,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,24; 84,5</t>
+          <t>69,8; 84,66</t>
         </is>
       </c>
     </row>
@@ -671,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56,97; 85,43</t>
+          <t>57,62; 85,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,77; 86,28</t>
+          <t>59,67; 86,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,81; 82,73</t>
+          <t>63,96; 83,19</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,5; 91,91</t>
+          <t>74,85; 91,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,82; 79,85</t>
+          <t>59,35; 80,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,79; 85,22</t>
+          <t>70,64; 85,03</t>
         </is>
       </c>
     </row>
@@ -771,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,43; 89,87</t>
+          <t>71,13; 89,25</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,26; 87,44</t>
+          <t>69,87; 88,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>74,04; 86,82</t>
+          <t>72,91; 86,06</t>
         </is>
       </c>
     </row>
@@ -821,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,55; 90,25</t>
+          <t>63,04; 89,92</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,39; 90,26</t>
+          <t>66,48; 89,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71,23; 87,95</t>
+          <t>70,94; 87,82</t>
         </is>
       </c>
     </row>
@@ -871,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,15; 83,29</t>
+          <t>72,89; 83,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,24; 79,08</t>
+          <t>70,2; 79,07</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>73,22; 79,54</t>
+          <t>72,98; 79,86</t>
         </is>
       </c>
     </row>
@@ -905,4 +906,602 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no está dispuesta a pagar para reducir el ruido (impuesto durante 5 años) (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>33601</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49797</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>83399</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>27517; 39009</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42270; 56162</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>73032; 92013</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>37418</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>38372</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75790</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>32358; 41547</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32737; 42856</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>67837; 82288</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>17879</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>28542</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>46421</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>14097; 20960</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22710; 32970</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>39988; 52015</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>100171</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>76464</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>176636</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>89944; 110341</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62852; 84824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>159680; 192207</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>40933</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>59843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>100776</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>35738; 44839</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>52011; 66040</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>90899; 107305</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>24670</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>32283</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56953</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>19476; 27778</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>26744; 36179</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>50452; 62458</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>348</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>254672</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>285302</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>539974</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>239294; 273873</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>266680; 300376</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>516831; 565561</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>50,88; 72,12</t>
+          <t>51,52; 72,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,28; 77,43</t>
+          <t>57,75; 77,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,68; 72,67</t>
+          <t>58,15; 72,35</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,8; 85,77</t>
+          <t>66,84; 85,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,15; 87,9</t>
+          <t>67,84; 86,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,8; 84,66</t>
+          <t>70,74; 84,75</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,62; 85,68</t>
+          <t>57,55; 84,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,67; 86,63</t>
+          <t>59,44; 86,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,96; 83,19</t>
+          <t>63,71; 83,0</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>74,85; 91,83</t>
+          <t>75,23; 92,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,35; 80,1</t>
+          <t>59,84; 80,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,64; 85,03</t>
+          <t>70,81; 85,55</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,13; 89,25</t>
+          <t>71,51; 89,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,87; 88,72</t>
+          <t>69,36; 87,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,91; 86,06</t>
+          <t>73,45; 86,03</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63,04; 89,92</t>
+          <t>65,42; 90,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,48; 89,93</t>
+          <t>66,51; 89,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70,94; 87,82</t>
+          <t>69,78; 86,99</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>72,89; 83,43</t>
+          <t>73,3; 83,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,2; 79,07</t>
+          <t>70,44; 79,13</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72,98; 79,86</t>
+          <t>72,91; 79,61</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27517; 39009</t>
+          <t>27865; 39070</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42270; 56162</t>
+          <t>41884; 56379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73032; 92013</t>
+          <t>73632; 91611</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32358; 41547</t>
+          <t>32377; 41490</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>32737; 42856</t>
+          <t>33078; 42407</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>67837; 82288</t>
+          <t>68752; 82369</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14097; 20960</t>
+          <t>14079; 20770</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22710; 32970</t>
+          <t>22623; 32798</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39988; 52015</t>
+          <t>39835; 51895</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>89944; 110341</t>
+          <t>90401; 110974</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62852; 84824</t>
+          <t>63366; 85262</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>159680; 192207</t>
+          <t>160072; 193394</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35738; 44839</t>
+          <t>35930; 44860</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>52011; 66040</t>
+          <t>51631; 65199</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>90899; 107305</t>
+          <t>91572; 107260</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19476; 27778</t>
+          <t>20208; 28021</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26744; 36179</t>
+          <t>26758; 36145</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50452; 62458</t>
+          <t>49629; 61871</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>239294; 273873</t>
+          <t>240636; 273230</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>266680; 300376</t>
+          <t>267597; 300609</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>516831; 565561</t>
+          <t>516359; 563799</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/RUIDO_1_R-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>68,66%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>51,52; 72,23</t>
+          <t>57,09; 76,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>57,75; 77,73</t>
+          <t>49,5; 72,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>58,15; 72,35</t>
+          <t>57,77; 71,92</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>77,25%</t>
+          <t>78,03%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,49%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>66,84; 85,66</t>
+          <t>65,36; 87,6</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,84; 86,98</t>
+          <t>64,75; 85,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,74; 84,75</t>
+          <t>69,68; 84,13</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>72,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,28%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57,55; 84,9</t>
+          <t>59,28; 84,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,44; 86,18</t>
+          <t>57,06; 85,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,71; 83,0</t>
+          <t>62,5; 81,64</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>77,82%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>75,23; 92,35</t>
+          <t>60,02; 79,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,84; 80,52</t>
+          <t>69,72; 84,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>70,81; 85,55</t>
+          <t>67,59; 80,03</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>80,83%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,51; 89,29</t>
+          <t>72,11; 88,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,36; 87,59</t>
+          <t>70,6; 89,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73,45; 86,03</t>
+          <t>75,28; 87,13</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>79,86%</t>
+          <t>78,97%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>80,08%</t>
+          <t>79,23%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>65,42; 90,71</t>
+          <t>64,48; 89,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>66,51; 89,85</t>
+          <t>62,5; 90,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>69,78; 86,99</t>
+          <t>70,05; 87,69</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>73,3; 83,23</t>
+          <t>70,33; 78,82</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>70,44; 79,13</t>
+          <t>70,12; 78,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>72,91; 79,61</t>
+          <t>71,89; 77,72</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>33601</t>
+          <t>46530</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>49797</t>
+          <t>33486</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83399</t>
+          <t>80016</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27865; 39070</t>
+          <t>39154; 52541</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41884; 56379</t>
+          <t>27069; 39560</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>73632; 91611</t>
+          <t>71211; 88654</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>37418</t>
+          <t>36722</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>38372</t>
+          <t>37791</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>75790</t>
+          <t>74512</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>32377; 41490</t>
+          <t>30761; 41228</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>33078; 42407</t>
+          <t>31787; 41853</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>68752; 82369</t>
+          <t>67003; 80899</t>
         </is>
       </c>
     </row>
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>17879</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28542</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>41661</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>14079; 20770</t>
+          <t>19408; 27822</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>22623; 32798</t>
+          <t>13757; 20576</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>39835; 51895</t>
+          <t>35531; 46415</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>110</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>100171</t>
+          <t>70283</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>76464</t>
+          <t>70656</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>176636</t>
+          <t>140939</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90401; 110974</t>
+          <t>58614; 77958</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>63366; 85262</t>
+          <t>63295; 76523</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>160072; 193394</t>
+          <t>127373; 150809</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>64</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40933</t>
+          <t>56682</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>59843</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100776</t>
+          <t>94457</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>35930; 44860</t>
+          <t>49653; 61027</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>51631; 65199</t>
+          <t>33026; 41772</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91572; 107260</t>
+          <t>87054; 100756</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>24670</t>
+          <t>29455</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>32283</t>
+          <t>25491</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56953</t>
+          <t>54946</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20208; 28021</t>
+          <t>24050; 33392</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26758; 36145</t>
+          <t>20029; 28937</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49629; 61871</t>
+          <t>48579; 60807</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>378</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>348</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>378</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>254672</t>
+          <t>263828</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>285302</t>
+          <t>222704</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>539974</t>
+          <t>486531</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>240636; 273230</t>
+          <t>247704; 277589</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>267597; 300609</t>
+          <t>208620; 234148</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>516359; 563799</t>
+          <t>467082; 504944</t>
         </is>
       </c>
     </row>
